--- a/4_pagos/efectivo/trazabilidad/trazabilidad_2026-08.xlsx
+++ b/4_pagos/efectivo/trazabilidad/trazabilidad_2026-08.xlsx
@@ -905,7 +905,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46244.30124661783</v>
+        <v>46244.30124662037</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -954,7 +954,7 @@
         <v>2</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46244.30124661783</v>
+        <v>46244.30124662037</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -1003,7 +1003,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46244.30124661783</v>
+        <v>46244.30124662037</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -1052,7 +1052,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46244.30124661783</v>
+        <v>46244.30124662037</v>
       </c>
     </row>
   </sheetData>
